--- a/models/Tarnoc_v2_base_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_base_2026-09-07.xlsx
@@ -1196,14 +1196,14 @@
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Base, EUR3m: 350 / 1,350 / 4,100 / 7,400 units in 2027 to 2030, EUR127m revenue in 2030. Gross margin 10%, 25%, 37%, 37%. EBITDA -2.5m, +0.8m, +18m, +34m. 95 people.</t>
+          <t>Base, EUR3m: 354 / 1,344 / 4,122 / 7,407 units in 2027 to 2030, EUR126m revenue in 2030. Gross margin 10%, 25%, 37%, 37%. EBITDA -2.5m, +0.9m, +17m, +34m. 95 people.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Cash low EUR0.6m in December 2027, about two months of cost; 81% of the raise used.</t>
+          <t xml:space="preserve">     Cash low EUR0.6m in December 2027, about two months of cost; 80% of the raise used.</t>
         </is>
       </c>
     </row>
@@ -22335,12 +22335,12 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Reps hired</t>
+          <t>Rep hiring rate</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>FTE/month</t>
         </is>
       </c>
       <c r="E16" s="64">
@@ -22605,7 +22605,7 @@
       </c>
       <c r="BT16" s="32" t="inlineStr">
         <is>
-          <t>no sales reps before the first month we can sell</t>
+          <t>the planned rate, which can be less than one a month</t>
         </is>
       </c>
     </row>
@@ -22621,243 +22621,243 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>Assumptions!$D$60+E16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:E16),0)</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>E17+F16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:F16),0)</f>
         <v/>
       </c>
       <c r="G17" s="13">
-        <f>F17+G16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:G16),0)</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>G17+H16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:H16),0)</f>
         <v/>
       </c>
       <c r="I17" s="13">
-        <f>H17+I16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:I16),0)</f>
         <v/>
       </c>
       <c r="J17" s="13">
-        <f>I17+J16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:J16),0)</f>
         <v/>
       </c>
       <c r="K17" s="13">
-        <f>J17+K16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:K16),0)</f>
         <v/>
       </c>
       <c r="L17" s="13">
-        <f>K17+L16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:L16),0)</f>
         <v/>
       </c>
       <c r="M17" s="13">
-        <f>L17+M16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:M16),0)</f>
         <v/>
       </c>
       <c r="N17" s="13">
-        <f>M17+N16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:N16),0)</f>
         <v/>
       </c>
       <c r="O17" s="13">
-        <f>N17+O16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:O16),0)</f>
         <v/>
       </c>
       <c r="P17" s="13">
-        <f>O17+P16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:P16),0)</f>
         <v/>
       </c>
       <c r="Q17" s="13">
-        <f>P17+Q16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:Q16),0)</f>
         <v/>
       </c>
       <c r="R17" s="13">
-        <f>Q17+R16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:R16),0)</f>
         <v/>
       </c>
       <c r="S17" s="13">
-        <f>R17+S16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:S16),0)</f>
         <v/>
       </c>
       <c r="T17" s="13">
-        <f>S17+T16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:T16),0)</f>
         <v/>
       </c>
       <c r="U17" s="13">
-        <f>T17+U16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:U16),0)</f>
         <v/>
       </c>
       <c r="V17" s="13">
-        <f>U17+V16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:V16),0)</f>
         <v/>
       </c>
       <c r="W17" s="13">
-        <f>V17+W16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:W16),0)</f>
         <v/>
       </c>
       <c r="X17" s="13">
-        <f>W17+X16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:X16),0)</f>
         <v/>
       </c>
       <c r="Y17" s="13">
-        <f>X17+Y16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:Y16),0)</f>
         <v/>
       </c>
       <c r="Z17" s="13">
-        <f>Y17+Z16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:Z16),0)</f>
         <v/>
       </c>
       <c r="AA17" s="13">
-        <f>Z17+AA16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AA16),0)</f>
         <v/>
       </c>
       <c r="AB17" s="13">
-        <f>AA17+AB16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AB16),0)</f>
         <v/>
       </c>
       <c r="AC17" s="13">
-        <f>AB17+AC16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AC16),0)</f>
         <v/>
       </c>
       <c r="AD17" s="13">
-        <f>AC17+AD16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AD16),0)</f>
         <v/>
       </c>
       <c r="AE17" s="13">
-        <f>AD17+AE16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AE16),0)</f>
         <v/>
       </c>
       <c r="AF17" s="13">
-        <f>AE17+AF16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AF16),0)</f>
         <v/>
       </c>
       <c r="AG17" s="13">
-        <f>AF17+AG16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AG16),0)</f>
         <v/>
       </c>
       <c r="AH17" s="13">
-        <f>AG17+AH16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AH16),0)</f>
         <v/>
       </c>
       <c r="AI17" s="13">
-        <f>AH17+AI16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AI16),0)</f>
         <v/>
       </c>
       <c r="AJ17" s="13">
-        <f>AI17+AJ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AJ16),0)</f>
         <v/>
       </c>
       <c r="AK17" s="13">
-        <f>AJ17+AK16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AK16),0)</f>
         <v/>
       </c>
       <c r="AL17" s="13">
-        <f>AK17+AL16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AL16),0)</f>
         <v/>
       </c>
       <c r="AM17" s="13">
-        <f>AL17+AM16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AM16),0)</f>
         <v/>
       </c>
       <c r="AN17" s="13">
-        <f>AM17+AN16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AN16),0)</f>
         <v/>
       </c>
       <c r="AO17" s="13">
-        <f>AN17+AO16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AO16),0)</f>
         <v/>
       </c>
       <c r="AP17" s="13">
-        <f>AO17+AP16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AP16),0)</f>
         <v/>
       </c>
       <c r="AQ17" s="13">
-        <f>AP17+AQ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AQ16),0)</f>
         <v/>
       </c>
       <c r="AR17" s="13">
-        <f>AQ17+AR16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AR16),0)</f>
         <v/>
       </c>
       <c r="AS17" s="13">
-        <f>AR17+AS16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AS16),0)</f>
         <v/>
       </c>
       <c r="AT17" s="13">
-        <f>AS17+AT16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AT16),0)</f>
         <v/>
       </c>
       <c r="AU17" s="13">
-        <f>AT17+AU16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AU16),0)</f>
         <v/>
       </c>
       <c r="AV17" s="13">
-        <f>AU17+AV16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AV16),0)</f>
         <v/>
       </c>
       <c r="AW17" s="13">
-        <f>AV17+AW16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AW16),0)</f>
         <v/>
       </c>
       <c r="AX17" s="13">
-        <f>AW17+AX16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AX16),0)</f>
         <v/>
       </c>
       <c r="AY17" s="13">
-        <f>AX17+AY16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AY16),0)</f>
         <v/>
       </c>
       <c r="AZ17" s="13">
-        <f>AY17+AZ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AZ16),0)</f>
         <v/>
       </c>
       <c r="BA17" s="13">
-        <f>AZ17+BA16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BA16),0)</f>
         <v/>
       </c>
       <c r="BB17" s="13">
-        <f>BA17+BB16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BB16),0)</f>
         <v/>
       </c>
       <c r="BC17" s="13">
-        <f>BB17+BC16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BC16),0)</f>
         <v/>
       </c>
       <c r="BD17" s="13">
-        <f>BC17+BD16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BD16),0)</f>
         <v/>
       </c>
       <c r="BE17" s="13">
-        <f>BD17+BE16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BE16),0)</f>
         <v/>
       </c>
       <c r="BF17" s="13">
-        <f>BE17+BF16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BF16),0)</f>
         <v/>
       </c>
       <c r="BG17" s="13">
-        <f>BF17+BG16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BG16),0)</f>
         <v/>
       </c>
       <c r="BH17" s="13">
-        <f>BG17+BH16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BH16),0)</f>
         <v/>
       </c>
       <c r="BI17" s="13">
-        <f>BH17+BI16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BI16),0)</f>
         <v/>
       </c>
       <c r="BJ17" s="13">
-        <f>BI17+BJ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BJ16),0)</f>
         <v/>
       </c>
       <c r="BK17" s="13">
-        <f>BJ17+BK16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BK16),0)</f>
         <v/>
       </c>
       <c r="BL17" s="13">
-        <f>BK17+BL16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BL16),0)</f>
         <v/>
       </c>
       <c r="BN17" s="66">
@@ -22880,6 +22880,11 @@
         <f>BL17</f>
         <v/>
       </c>
+      <c r="BT17" s="32" t="inlineStr">
+        <is>
+          <t>whole people only, so half a rep a month means one every second month</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
@@ -23161,277 +23166,277 @@
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Installer partners signed</t>
+          <t>Partner signing rate</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>partners</t>
-        </is>
-      </c>
-      <c r="E19" s="13">
+          <t>partners/month</t>
+        </is>
+      </c>
+      <c r="E19" s="64">
         <f>IF(E$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(E$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="64">
         <f>IF(F$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(F$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="64">
         <f>IF(G$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(G$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="64">
         <f>IF(H$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(H$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="64">
         <f>IF(I$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(I$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="64">
         <f>IF(J$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(J$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="64">
         <f>IF(K$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(K$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="64">
         <f>IF(L$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(L$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="64">
         <f>IF(M$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(M$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="64">
         <f>IF(N$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(N$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="O19" s="13">
+      <c r="O19" s="64">
         <f>IF(O$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(O$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P19" s="13">
+      <c r="P19" s="64">
         <f>IF(P$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(P$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="Q19" s="13">
+      <c r="Q19" s="64">
         <f>IF(Q$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(Q$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="R19" s="13">
+      <c r="R19" s="64">
         <f>IF(R$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(R$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="64">
         <f>IF(S$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(S$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="64">
         <f>IF(T$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(T$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="U19" s="13">
+      <c r="U19" s="64">
         <f>IF(U$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(U$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="V19" s="13">
+      <c r="V19" s="64">
         <f>IF(V$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(V$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="64">
         <f>IF(W$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(W$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="X19" s="13">
+      <c r="X19" s="64">
         <f>IF(X$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(X$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="Y19" s="13">
+      <c r="Y19" s="64">
         <f>IF(Y$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(Y$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="64">
         <f>IF(Z$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(Z$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AA19" s="13">
+      <c r="AA19" s="64">
         <f>IF(AA$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AA$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AB19" s="13">
+      <c r="AB19" s="64">
         <f>IF(AB$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AB$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AC19" s="13">
+      <c r="AC19" s="64">
         <f>IF(AC$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AC$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AD19" s="13">
+      <c r="AD19" s="64">
         <f>IF(AD$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AD$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AE19" s="13">
+      <c r="AE19" s="64">
         <f>IF(AE$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AE$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AF19" s="13">
+      <c r="AF19" s="64">
         <f>IF(AF$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AF$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AG19" s="13">
+      <c r="AG19" s="64">
         <f>IF(AG$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AG$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AH19" s="13">
+      <c r="AH19" s="64">
         <f>IF(AH$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AH$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AI19" s="13">
+      <c r="AI19" s="64">
         <f>IF(AI$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AI$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AJ19" s="13">
+      <c r="AJ19" s="64">
         <f>IF(AJ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AJ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AK19" s="13">
+      <c r="AK19" s="64">
         <f>IF(AK$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AK$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AL19" s="13">
+      <c r="AL19" s="64">
         <f>IF(AL$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AL$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AM19" s="13">
+      <c r="AM19" s="64">
         <f>IF(AM$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AM$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AN19" s="13">
+      <c r="AN19" s="64">
         <f>IF(AN$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AN$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AO19" s="13">
+      <c r="AO19" s="64">
         <f>IF(AO$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AO$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AP19" s="13">
+      <c r="AP19" s="64">
         <f>IF(AP$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AP$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AQ19" s="13">
+      <c r="AQ19" s="64">
         <f>IF(AQ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AQ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AR19" s="13">
+      <c r="AR19" s="64">
         <f>IF(AR$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AR$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AS19" s="13">
+      <c r="AS19" s="64">
         <f>IF(AS$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AS$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AT19" s="13">
+      <c r="AT19" s="64">
         <f>IF(AT$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AT$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AU19" s="13">
+      <c r="AU19" s="64">
         <f>IF(AU$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AU$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AV19" s="13">
+      <c r="AV19" s="64">
         <f>IF(AV$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AV$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AW19" s="13">
+      <c r="AW19" s="64">
         <f>IF(AW$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AW$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AX19" s="13">
+      <c r="AX19" s="64">
         <f>IF(AX$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AX$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AY19" s="13">
+      <c r="AY19" s="64">
         <f>IF(AY$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AY$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AZ19" s="13">
+      <c r="AZ19" s="64">
         <f>IF(AZ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AZ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BA19" s="13">
+      <c r="BA19" s="64">
         <f>IF(BA$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BA$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BB19" s="13">
+      <c r="BB19" s="64">
         <f>IF(BB$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BB$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BC19" s="13">
+      <c r="BC19" s="64">
         <f>IF(BC$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BC$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BD19" s="13">
+      <c r="BD19" s="64">
         <f>IF(BD$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BD$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BE19" s="13">
+      <c r="BE19" s="64">
         <f>IF(BE$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BE$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BF19" s="13">
+      <c r="BF19" s="64">
         <f>IF(BF$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BF$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BG19" s="13">
+      <c r="BG19" s="64">
         <f>IF(BG$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BG$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BH19" s="13">
+      <c r="BH19" s="64">
         <f>IF(BH$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BH$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BI19" s="13">
+      <c r="BI19" s="64">
         <f>IF(BI$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BI$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BJ19" s="13">
+      <c r="BJ19" s="64">
         <f>IF(BJ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BJ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BK19" s="13">
+      <c r="BK19" s="64">
         <f>IF(BK$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BK$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BL19" s="13">
+      <c r="BL19" s="64">
         <f>IF(BL$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BL$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BN19" s="66">
+      <c r="BN19" s="65">
         <f>SUM(E19:P19)</f>
         <v/>
       </c>
-      <c r="BO19" s="66">
+      <c r="BO19" s="65">
         <f>SUM(Q19:AB19)</f>
         <v/>
       </c>
-      <c r="BP19" s="66">
+      <c r="BP19" s="65">
         <f>SUM(AC19:AN19)</f>
         <v/>
       </c>
-      <c r="BQ19" s="66">
+      <c r="BQ19" s="65">
         <f>SUM(AO19:AZ19)</f>
         <v/>
       </c>
-      <c r="BR19" s="66">
+      <c r="BR19" s="65">
         <f>SUM(BA19:BL19)</f>
         <v/>
       </c>
       <c r="BT19" s="32" t="inlineStr">
         <is>
-          <t>no partner intros before the first month we can sell</t>
+          <t>the planned rate, which can be less than one a month</t>
         </is>
       </c>
     </row>
@@ -23447,243 +23452,243 @@
         </is>
       </c>
       <c r="E20" s="13">
-        <f>Assumptions!$D$62+E19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:E19),0)</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>E20+F19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:F19),0)</f>
         <v/>
       </c>
       <c r="G20" s="13">
-        <f>F20+G19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:G19),0)</f>
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>G20+H19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:H19),0)</f>
         <v/>
       </c>
       <c r="I20" s="13">
-        <f>H20+I19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:I19),0)</f>
         <v/>
       </c>
       <c r="J20" s="13">
-        <f>I20+J19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:J19),0)</f>
         <v/>
       </c>
       <c r="K20" s="13">
-        <f>J20+K19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:K19),0)</f>
         <v/>
       </c>
       <c r="L20" s="13">
-        <f>K20+L19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:L19),0)</f>
         <v/>
       </c>
       <c r="M20" s="13">
-        <f>L20+M19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:M19),0)</f>
         <v/>
       </c>
       <c r="N20" s="13">
-        <f>M20+N19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:N19),0)</f>
         <v/>
       </c>
       <c r="O20" s="13">
-        <f>N20+O19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:O19),0)</f>
         <v/>
       </c>
       <c r="P20" s="13">
-        <f>O20+P19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:P19),0)</f>
         <v/>
       </c>
       <c r="Q20" s="13">
-        <f>P20+Q19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:Q19),0)</f>
         <v/>
       </c>
       <c r="R20" s="13">
-        <f>Q20+R19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:R19),0)</f>
         <v/>
       </c>
       <c r="S20" s="13">
-        <f>R20+S19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:S19),0)</f>
         <v/>
       </c>
       <c r="T20" s="13">
-        <f>S20+T19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:T19),0)</f>
         <v/>
       </c>
       <c r="U20" s="13">
-        <f>T20+U19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:U19),0)</f>
         <v/>
       </c>
       <c r="V20" s="13">
-        <f>U20+V19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:V19),0)</f>
         <v/>
       </c>
       <c r="W20" s="13">
-        <f>V20+W19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:W19),0)</f>
         <v/>
       </c>
       <c r="X20" s="13">
-        <f>W20+X19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:X19),0)</f>
         <v/>
       </c>
       <c r="Y20" s="13">
-        <f>X20+Y19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:Y19),0)</f>
         <v/>
       </c>
       <c r="Z20" s="13">
-        <f>Y20+Z19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:Z19),0)</f>
         <v/>
       </c>
       <c r="AA20" s="13">
-        <f>Z20+AA19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AA19),0)</f>
         <v/>
       </c>
       <c r="AB20" s="13">
-        <f>AA20+AB19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AB19),0)</f>
         <v/>
       </c>
       <c r="AC20" s="13">
-        <f>AB20+AC19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AC19),0)</f>
         <v/>
       </c>
       <c r="AD20" s="13">
-        <f>AC20+AD19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AD19),0)</f>
         <v/>
       </c>
       <c r="AE20" s="13">
-        <f>AD20+AE19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AE19),0)</f>
         <v/>
       </c>
       <c r="AF20" s="13">
-        <f>AE20+AF19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AF19),0)</f>
         <v/>
       </c>
       <c r="AG20" s="13">
-        <f>AF20+AG19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AG19),0)</f>
         <v/>
       </c>
       <c r="AH20" s="13">
-        <f>AG20+AH19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AH19),0)</f>
         <v/>
       </c>
       <c r="AI20" s="13">
-        <f>AH20+AI19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AI19),0)</f>
         <v/>
       </c>
       <c r="AJ20" s="13">
-        <f>AI20+AJ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AJ19),0)</f>
         <v/>
       </c>
       <c r="AK20" s="13">
-        <f>AJ20+AK19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AK19),0)</f>
         <v/>
       </c>
       <c r="AL20" s="13">
-        <f>AK20+AL19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AL19),0)</f>
         <v/>
       </c>
       <c r="AM20" s="13">
-        <f>AL20+AM19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AM19),0)</f>
         <v/>
       </c>
       <c r="AN20" s="13">
-        <f>AM20+AN19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AN19),0)</f>
         <v/>
       </c>
       <c r="AO20" s="13">
-        <f>AN20+AO19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AO19),0)</f>
         <v/>
       </c>
       <c r="AP20" s="13">
-        <f>AO20+AP19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AP19),0)</f>
         <v/>
       </c>
       <c r="AQ20" s="13">
-        <f>AP20+AQ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AQ19),0)</f>
         <v/>
       </c>
       <c r="AR20" s="13">
-        <f>AQ20+AR19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AR19),0)</f>
         <v/>
       </c>
       <c r="AS20" s="13">
-        <f>AR20+AS19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AS19),0)</f>
         <v/>
       </c>
       <c r="AT20" s="13">
-        <f>AS20+AT19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AT19),0)</f>
         <v/>
       </c>
       <c r="AU20" s="13">
-        <f>AT20+AU19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AU19),0)</f>
         <v/>
       </c>
       <c r="AV20" s="13">
-        <f>AU20+AV19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AV19),0)</f>
         <v/>
       </c>
       <c r="AW20" s="13">
-        <f>AV20+AW19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AW19),0)</f>
         <v/>
       </c>
       <c r="AX20" s="13">
-        <f>AW20+AX19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AX19),0)</f>
         <v/>
       </c>
       <c r="AY20" s="13">
-        <f>AX20+AY19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AY19),0)</f>
         <v/>
       </c>
       <c r="AZ20" s="13">
-        <f>AY20+AZ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AZ19),0)</f>
         <v/>
       </c>
       <c r="BA20" s="13">
-        <f>AZ20+BA19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BA19),0)</f>
         <v/>
       </c>
       <c r="BB20" s="13">
-        <f>BA20+BB19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BB19),0)</f>
         <v/>
       </c>
       <c r="BC20" s="13">
-        <f>BB20+BC19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BC19),0)</f>
         <v/>
       </c>
       <c r="BD20" s="13">
-        <f>BC20+BD19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BD19),0)</f>
         <v/>
       </c>
       <c r="BE20" s="13">
-        <f>BD20+BE19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BE19),0)</f>
         <v/>
       </c>
       <c r="BF20" s="13">
-        <f>BE20+BF19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BF19),0)</f>
         <v/>
       </c>
       <c r="BG20" s="13">
-        <f>BF20+BG19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BG19),0)</f>
         <v/>
       </c>
       <c r="BH20" s="13">
-        <f>BG20+BH19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BH19),0)</f>
         <v/>
       </c>
       <c r="BI20" s="13">
-        <f>BH20+BI19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BI19),0)</f>
         <v/>
       </c>
       <c r="BJ20" s="13">
-        <f>BI20+BJ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BJ19),0)</f>
         <v/>
       </c>
       <c r="BK20" s="13">
-        <f>BJ20+BK19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BK19),0)</f>
         <v/>
       </c>
       <c r="BL20" s="13">
-        <f>BK20+BL19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BL19),0)</f>
         <v/>
       </c>
       <c r="BN20" s="66">
@@ -23705,6 +23710,11 @@
       <c r="BR20" s="66">
         <f>BL20</f>
         <v/>
+      </c>
+      <c r="BT20" s="32" t="inlineStr">
+        <is>
+          <t>whole partners only, signed as the running total passes each whole number</t>
+        </is>
       </c>
     </row>
     <row r="21">

--- a/models/Tarnoc_v2_base_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_base_2026-09-07.xlsx
@@ -26156,243 +26156,243 @@
         </is>
       </c>
       <c r="E39" s="9">
-        <f>E34*Assumptions!$D$25</f>
+        <f>ROUND(E34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>F34*Assumptions!$D$25</f>
+        <f>ROUND(F34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="G39" s="9">
-        <f>G34*Assumptions!$D$25</f>
+        <f>ROUND(G34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="H39" s="9">
-        <f>H34*Assumptions!$D$25</f>
+        <f>ROUND(H34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="I39" s="9">
-        <f>I34*Assumptions!$D$25</f>
+        <f>ROUND(I34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="J39" s="9">
-        <f>J34*Assumptions!$D$25</f>
+        <f>ROUND(J34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>K34*Assumptions!$D$25</f>
+        <f>ROUND(K34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="L39" s="9">
-        <f>L34*Assumptions!$D$25</f>
+        <f>ROUND(L34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="M39" s="9">
-        <f>M34*Assumptions!$D$25</f>
+        <f>ROUND(M34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="N39" s="9">
-        <f>N34*Assumptions!$D$25</f>
+        <f>ROUND(N34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="O39" s="9">
-        <f>O34*Assumptions!$D$25</f>
+        <f>ROUND(O34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="P39" s="9">
-        <f>P34*Assumptions!$D$25</f>
+        <f>ROUND(P34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="Q39" s="9">
-        <f>Q34*Assumptions!$D$25</f>
+        <f>ROUND(Q34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="R39" s="9">
-        <f>R34*Assumptions!$D$25</f>
+        <f>ROUND(R34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="S39" s="9">
-        <f>S34*Assumptions!$D$25</f>
+        <f>ROUND(S34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="T39" s="9">
-        <f>T34*Assumptions!$D$25</f>
+        <f>ROUND(T34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="U39" s="9">
-        <f>U34*Assumptions!$D$25</f>
+        <f>ROUND(U34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="V39" s="9">
-        <f>V34*Assumptions!$D$25</f>
+        <f>ROUND(V34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="W39" s="9">
-        <f>W34*Assumptions!$D$25</f>
+        <f>ROUND(W34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="X39" s="9">
-        <f>X34*Assumptions!$D$25</f>
+        <f>ROUND(X34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="Y39" s="9">
-        <f>Y34*Assumptions!$D$25</f>
+        <f>ROUND(Y34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="Z39" s="9">
-        <f>Z34*Assumptions!$D$25</f>
+        <f>ROUND(Z34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AA39" s="9">
-        <f>AA34*Assumptions!$D$25</f>
+        <f>ROUND(AA34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AB39" s="9">
-        <f>AB34*Assumptions!$D$25</f>
+        <f>ROUND(AB34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AC39" s="9">
-        <f>AC34*Assumptions!$D$25</f>
+        <f>ROUND(AC34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AD39" s="9">
-        <f>AD34*Assumptions!$D$25</f>
+        <f>ROUND(AD34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AE39" s="9">
-        <f>AE34*Assumptions!$D$25</f>
+        <f>ROUND(AE34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AF39" s="9">
-        <f>AF34*Assumptions!$D$25</f>
+        <f>ROUND(AF34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AG39" s="9">
-        <f>AG34*Assumptions!$D$25</f>
+        <f>ROUND(AG34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AH39" s="9">
-        <f>AH34*Assumptions!$D$25</f>
+        <f>ROUND(AH34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AI39" s="9">
-        <f>AI34*Assumptions!$D$25</f>
+        <f>ROUND(AI34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AJ39" s="9">
-        <f>AJ34*Assumptions!$D$25</f>
+        <f>ROUND(AJ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AK39" s="9">
-        <f>AK34*Assumptions!$D$25</f>
+        <f>ROUND(AK34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AL39" s="9">
-        <f>AL34*Assumptions!$D$25</f>
+        <f>ROUND(AL34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AM39" s="9">
-        <f>AM34*Assumptions!$D$25</f>
+        <f>ROUND(AM34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AN39" s="9">
-        <f>AN34*Assumptions!$D$25</f>
+        <f>ROUND(AN34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AO39" s="9">
-        <f>AO34*Assumptions!$D$25</f>
+        <f>ROUND(AO34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AP39" s="9">
-        <f>AP34*Assumptions!$D$25</f>
+        <f>ROUND(AP34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AQ39" s="9">
-        <f>AQ34*Assumptions!$D$25</f>
+        <f>ROUND(AQ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AR39" s="9">
-        <f>AR34*Assumptions!$D$25</f>
+        <f>ROUND(AR34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AS39" s="9">
-        <f>AS34*Assumptions!$D$25</f>
+        <f>ROUND(AS34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AT39" s="9">
-        <f>AT34*Assumptions!$D$25</f>
+        <f>ROUND(AT34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AU39" s="9">
-        <f>AU34*Assumptions!$D$25</f>
+        <f>ROUND(AU34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AV39" s="9">
-        <f>AV34*Assumptions!$D$25</f>
+        <f>ROUND(AV34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AW39" s="9">
-        <f>AW34*Assumptions!$D$25</f>
+        <f>ROUND(AW34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AX39" s="9">
-        <f>AX34*Assumptions!$D$25</f>
+        <f>ROUND(AX34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AY39" s="9">
-        <f>AY34*Assumptions!$D$25</f>
+        <f>ROUND(AY34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AZ39" s="9">
-        <f>AZ34*Assumptions!$D$25</f>
+        <f>ROUND(AZ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BA39" s="9">
-        <f>BA34*Assumptions!$D$25</f>
+        <f>ROUND(BA34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BB39" s="9">
-        <f>BB34*Assumptions!$D$25</f>
+        <f>ROUND(BB34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BC39" s="9">
-        <f>BC34*Assumptions!$D$25</f>
+        <f>ROUND(BC34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BD39" s="9">
-        <f>BD34*Assumptions!$D$25</f>
+        <f>ROUND(BD34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BE39" s="9">
-        <f>BE34*Assumptions!$D$25</f>
+        <f>ROUND(BE34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BF39" s="9">
-        <f>BF34*Assumptions!$D$25</f>
+        <f>ROUND(BF34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BG39" s="9">
-        <f>BG34*Assumptions!$D$25</f>
+        <f>ROUND(BG34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BH39" s="9">
-        <f>BH34*Assumptions!$D$25</f>
+        <f>ROUND(BH34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BI39" s="9">
-        <f>BI34*Assumptions!$D$25</f>
+        <f>ROUND(BI34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BJ39" s="9">
-        <f>BJ34*Assumptions!$D$25</f>
+        <f>ROUND(BJ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BK39" s="9">
-        <f>BK34*Assumptions!$D$25</f>
+        <f>ROUND(BK34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BL39" s="9">
-        <f>BL34*Assumptions!$D$25</f>
+        <f>ROUND(BL34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BN39" s="60">
@@ -26415,6 +26415,11 @@
         <f>SUM(BA39:BL39)</f>
         <v/>
       </c>
+      <c r="BT39" s="32" t="inlineStr">
+        <is>
+          <t>whole units, and the Combi+ row takes the remainder so the two add to units sold</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
@@ -26428,243 +26433,243 @@
         </is>
       </c>
       <c r="E40" s="9">
-        <f>E34*Assumptions!$D$26</f>
+        <f>E34-E39</f>
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>F34*Assumptions!$D$26</f>
+        <f>F34-F39</f>
         <v/>
       </c>
       <c r="G40" s="9">
-        <f>G34*Assumptions!$D$26</f>
+        <f>G34-G39</f>
         <v/>
       </c>
       <c r="H40" s="9">
-        <f>H34*Assumptions!$D$26</f>
+        <f>H34-H39</f>
         <v/>
       </c>
       <c r="I40" s="9">
-        <f>I34*Assumptions!$D$26</f>
+        <f>I34-I39</f>
         <v/>
       </c>
       <c r="J40" s="9">
-        <f>J34*Assumptions!$D$26</f>
+        <f>J34-J39</f>
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>K34*Assumptions!$D$26</f>
+        <f>K34-K39</f>
         <v/>
       </c>
       <c r="L40" s="9">
-        <f>L34*Assumptions!$D$26</f>
+        <f>L34-L39</f>
         <v/>
       </c>
       <c r="M40" s="9">
-        <f>M34*Assumptions!$D$26</f>
+        <f>M34-M39</f>
         <v/>
       </c>
       <c r="N40" s="9">
-        <f>N34*Assumptions!$D$26</f>
+        <f>N34-N39</f>
         <v/>
       </c>
       <c r="O40" s="9">
-        <f>O34*Assumptions!$D$26</f>
+        <f>O34-O39</f>
         <v/>
       </c>
       <c r="P40" s="9">
-        <f>P34*Assumptions!$D$26</f>
+        <f>P34-P39</f>
         <v/>
       </c>
       <c r="Q40" s="9">
-        <f>Q34*Assumptions!$D$26</f>
+        <f>Q34-Q39</f>
         <v/>
       </c>
       <c r="R40" s="9">
-        <f>R34*Assumptions!$D$26</f>
+        <f>R34-R39</f>
         <v/>
       </c>
       <c r="S40" s="9">
-        <f>S34*Assumptions!$D$26</f>
+        <f>S34-S39</f>
         <v/>
       </c>
       <c r="T40" s="9">
-        <f>T34*Assumptions!$D$26</f>
+        <f>T34-T39</f>
         <v/>
       </c>
       <c r="U40" s="9">
-        <f>U34*Assumptions!$D$26</f>
+        <f>U34-U39</f>
         <v/>
       </c>
       <c r="V40" s="9">
-        <f>V34*Assumptions!$D$26</f>
+        <f>V34-V39</f>
         <v/>
       </c>
       <c r="W40" s="9">
-        <f>W34*Assumptions!$D$26</f>
+        <f>W34-W39</f>
         <v/>
       </c>
       <c r="X40" s="9">
-        <f>X34*Assumptions!$D$26</f>
+        <f>X34-X39</f>
         <v/>
       </c>
       <c r="Y40" s="9">
-        <f>Y34*Assumptions!$D$26</f>
+        <f>Y34-Y39</f>
         <v/>
       </c>
       <c r="Z40" s="9">
-        <f>Z34*Assumptions!$D$26</f>
+        <f>Z34-Z39</f>
         <v/>
       </c>
       <c r="AA40" s="9">
-        <f>AA34*Assumptions!$D$26</f>
+        <f>AA34-AA39</f>
         <v/>
       </c>
       <c r="AB40" s="9">
-        <f>AB34*Assumptions!$D$26</f>
+        <f>AB34-AB39</f>
         <v/>
       </c>
       <c r="AC40" s="9">
-        <f>AC34*Assumptions!$D$26</f>
+        <f>AC34-AC39</f>
         <v/>
       </c>
       <c r="AD40" s="9">
-        <f>AD34*Assumptions!$D$26</f>
+        <f>AD34-AD39</f>
         <v/>
       </c>
       <c r="AE40" s="9">
-        <f>AE34*Assumptions!$D$26</f>
+        <f>AE34-AE39</f>
         <v/>
       </c>
       <c r="AF40" s="9">
-        <f>AF34*Assumptions!$D$26</f>
+        <f>AF34-AF39</f>
         <v/>
       </c>
       <c r="AG40" s="9">
-        <f>AG34*Assumptions!$D$26</f>
+        <f>AG34-AG39</f>
         <v/>
       </c>
       <c r="AH40" s="9">
-        <f>AH34*Assumptions!$D$26</f>
+        <f>AH34-AH39</f>
         <v/>
       </c>
       <c r="AI40" s="9">
-        <f>AI34*Assumptions!$D$26</f>
+        <f>AI34-AI39</f>
         <v/>
       </c>
       <c r="AJ40" s="9">
-        <f>AJ34*Assumptions!$D$26</f>
+        <f>AJ34-AJ39</f>
         <v/>
       </c>
       <c r="AK40" s="9">
-        <f>AK34*Assumptions!$D$26</f>
+        <f>AK34-AK39</f>
         <v/>
       </c>
       <c r="AL40" s="9">
-        <f>AL34*Assumptions!$D$26</f>
+        <f>AL34-AL39</f>
         <v/>
       </c>
       <c r="AM40" s="9">
-        <f>AM34*Assumptions!$D$26</f>
+        <f>AM34-AM39</f>
         <v/>
       </c>
       <c r="AN40" s="9">
-        <f>AN34*Assumptions!$D$26</f>
+        <f>AN34-AN39</f>
         <v/>
       </c>
       <c r="AO40" s="9">
-        <f>AO34*Assumptions!$D$26</f>
+        <f>AO34-AO39</f>
         <v/>
       </c>
       <c r="AP40" s="9">
-        <f>AP34*Assumptions!$D$26</f>
+        <f>AP34-AP39</f>
         <v/>
       </c>
       <c r="AQ40" s="9">
-        <f>AQ34*Assumptions!$D$26</f>
+        <f>AQ34-AQ39</f>
         <v/>
       </c>
       <c r="AR40" s="9">
-        <f>AR34*Assumptions!$D$26</f>
+        <f>AR34-AR39</f>
         <v/>
       </c>
       <c r="AS40" s="9">
-        <f>AS34*Assumptions!$D$26</f>
+        <f>AS34-AS39</f>
         <v/>
       </c>
       <c r="AT40" s="9">
-        <f>AT34*Assumptions!$D$26</f>
+        <f>AT34-AT39</f>
         <v/>
       </c>
       <c r="AU40" s="9">
-        <f>AU34*Assumptions!$D$26</f>
+        <f>AU34-AU39</f>
         <v/>
       </c>
       <c r="AV40" s="9">
-        <f>AV34*Assumptions!$D$26</f>
+        <f>AV34-AV39</f>
         <v/>
       </c>
       <c r="AW40" s="9">
-        <f>AW34*Assumptions!$D$26</f>
+        <f>AW34-AW39</f>
         <v/>
       </c>
       <c r="AX40" s="9">
-        <f>AX34*Assumptions!$D$26</f>
+        <f>AX34-AX39</f>
         <v/>
       </c>
       <c r="AY40" s="9">
-        <f>AY34*Assumptions!$D$26</f>
+        <f>AY34-AY39</f>
         <v/>
       </c>
       <c r="AZ40" s="9">
-        <f>AZ34*Assumptions!$D$26</f>
+        <f>AZ34-AZ39</f>
         <v/>
       </c>
       <c r="BA40" s="9">
-        <f>BA34*Assumptions!$D$26</f>
+        <f>BA34-BA39</f>
         <v/>
       </c>
       <c r="BB40" s="9">
-        <f>BB34*Assumptions!$D$26</f>
+        <f>BB34-BB39</f>
         <v/>
       </c>
       <c r="BC40" s="9">
-        <f>BC34*Assumptions!$D$26</f>
+        <f>BC34-BC39</f>
         <v/>
       </c>
       <c r="BD40" s="9">
-        <f>BD34*Assumptions!$D$26</f>
+        <f>BD34-BD39</f>
         <v/>
       </c>
       <c r="BE40" s="9">
-        <f>BE34*Assumptions!$D$26</f>
+        <f>BE34-BE39</f>
         <v/>
       </c>
       <c r="BF40" s="9">
-        <f>BF34*Assumptions!$D$26</f>
+        <f>BF34-BF39</f>
         <v/>
       </c>
       <c r="BG40" s="9">
-        <f>BG34*Assumptions!$D$26</f>
+        <f>BG34-BG39</f>
         <v/>
       </c>
       <c r="BH40" s="9">
-        <f>BH34*Assumptions!$D$26</f>
+        <f>BH34-BH39</f>
         <v/>
       </c>
       <c r="BI40" s="9">
-        <f>BI34*Assumptions!$D$26</f>
+        <f>BI34-BI39</f>
         <v/>
       </c>
       <c r="BJ40" s="9">
-        <f>BJ34*Assumptions!$D$26</f>
+        <f>BJ34-BJ39</f>
         <v/>
       </c>
       <c r="BK40" s="9">
-        <f>BK34*Assumptions!$D$26</f>
+        <f>BK34-BK39</f>
         <v/>
       </c>
       <c r="BL40" s="9">
-        <f>BL34*Assumptions!$D$26</f>
+        <f>BL34-BL39</f>
         <v/>
       </c>
       <c r="BN40" s="60">

--- a/models/Tarnoc_v2_base_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_base_2026-09-07.xlsx
@@ -186,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -537,6 +537,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -9148,7 +9151,7 @@
       </c>
       <c r="G5" s="87" t="inlineStr">
         <is>
-          <t>Sets the tier 2 and tier 3 prices. There is no supplier quote for any of the three tiers.</t>
+          <t>Sets the tier 2 and tier 3 prices. Tier 1 is EUR9,984. There is no supplier quote for any of the three tiers.</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9216,7 @@
         <v>0.4</v>
       </c>
       <c r="E8" s="39" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="G8" s="87" t="inlineStr">
         <is>
@@ -9229,22 +9232,22 @@
       </c>
       <c r="C9" s="86" t="inlineStr">
         <is>
-          <t>0.8 to 2.9</t>
+          <t>0.75 to 2.85</t>
         </is>
       </c>
       <c r="D9" s="86" t="inlineStr">
         <is>
-          <t>1.0 to 3.8</t>
+          <t>1 to 3.8</t>
         </is>
       </c>
       <c r="E9" s="86" t="inlineStr">
         <is>
-          <t>1.3 to 4.8</t>
+          <t>1.25 to 4.75</t>
         </is>
       </c>
       <c r="G9" s="87" t="inlineStr">
         <is>
-          <t>The plan reaches 113 partners on the books by the end of 2030.</t>
+          <t>Downside signs 75% of the plan, upside 125%.</t>
         </is>
       </c>
     </row>
@@ -9288,11 +9291,11 @@
         <v>650</v>
       </c>
       <c r="E11" s="88" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G11" s="87" t="inlineStr">
         <is>
-          <t>At 650 a month the partner limits volume in 2030.</t>
+          <t>At 650 a month the partner limits volume from August 2030.</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9306,7 @@
         </is>
       </c>
       <c r="C12" s="88" t="n">
-        <v>8000</v>
+        <v>8014</v>
       </c>
       <c r="D12" s="88" t="n">
         <v>8526</v>
@@ -9354,7 +9357,7 @@
         <v>354</v>
       </c>
       <c r="E15" s="79" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16">
@@ -9364,13 +9367,13 @@
         </is>
       </c>
       <c r="C16" s="79" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D16" s="79" t="n">
         <v>1344</v>
       </c>
       <c r="E16" s="79" t="n">
-        <v>2447</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="17">
@@ -9380,13 +9383,13 @@
         </is>
       </c>
       <c r="C17" s="79" t="n">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="D17" s="79" t="n">
         <v>4122</v>
       </c>
       <c r="E17" s="79" t="n">
-        <v>7468</v>
+        <v>7478</v>
       </c>
     </row>
     <row r="18">
@@ -9396,13 +9399,13 @@
         </is>
       </c>
       <c r="C18" s="79" t="n">
-        <v>3391</v>
+        <v>3405</v>
       </c>
       <c r="D18" s="79" t="n">
         <v>7407</v>
       </c>
       <c r="E18" s="79" t="n">
-        <v>11333</v>
+        <v>11334</v>
       </c>
     </row>
     <row r="19">
@@ -9412,13 +9415,13 @@
         </is>
       </c>
       <c r="C19" s="79" t="n">
-        <v>5976</v>
+        <v>6001</v>
       </c>
       <c r="D19" s="79" t="n">
         <v>13227</v>
       </c>
       <c r="E19" s="79" t="n">
-        <v>21868</v>
+        <v>21883</v>
       </c>
     </row>
     <row r="20">
@@ -9428,13 +9431,13 @@
         </is>
       </c>
       <c r="C20" s="90" t="n">
-        <v>2428</v>
+        <v>2439</v>
       </c>
       <c r="D20" s="90" t="n">
         <v>5466</v>
       </c>
       <c r="E20" s="90" t="n">
-        <v>9915</v>
+        <v>9926</v>
       </c>
       <c r="G20" s="87" t="inlineStr">
         <is>
@@ -9465,7 +9468,7 @@
       </c>
       <c r="G21" s="87" t="inlineStr">
         <is>
-          <t>Below 5,000 the 2028 BOM is EUR9,984 a unit instead of EUR7,069.</t>
+          <t>Below 5,000 the 2028 BOM is charged at the tier 1 price.</t>
         </is>
       </c>
     </row>
@@ -9500,13 +9503,13 @@
         </is>
       </c>
       <c r="C24" s="79" t="n">
-        <v>57444957</v>
+        <v>57697399</v>
       </c>
       <c r="D24" s="79" t="n">
         <v>126282824</v>
       </c>
       <c r="E24" s="79" t="n">
-        <v>193451900</v>
+        <v>193472874</v>
       </c>
     </row>
     <row r="25">
@@ -9516,17 +9519,17 @@
         </is>
       </c>
       <c r="C25" s="94" t="n">
-        <v>0.1520679866288649</v>
+        <v>0.1522400393329175</v>
       </c>
       <c r="D25" s="94" t="n">
         <v>0.3674427916398863</v>
       </c>
       <c r="E25" s="94" t="n">
-        <v>0.3676093317437056</v>
+        <v>0.3676145188616465</v>
       </c>
       <c r="G25" s="87" t="inlineStr">
         <is>
-          <t>The downside stays below 5,000 units, so it is charged the tier 1 BOM in every year.</t>
+          <t>A case that never passes 5,000 units is charged the tier 1 BOM in every year.</t>
         </is>
       </c>
     </row>
@@ -9536,14 +9539,14 @@
           <t>EBITDA 2027</t>
         </is>
       </c>
-      <c r="C26" s="79" t="n">
-        <v>-2729582</v>
-      </c>
-      <c r="D26" s="79" t="n">
+      <c r="C26" s="97" t="n">
+        <v>-2729157</v>
+      </c>
+      <c r="D26" s="97" t="n">
         <v>-2495962</v>
       </c>
-      <c r="E26" s="79" t="n">
-        <v>-2255860</v>
+      <c r="E26" s="97" t="n">
+        <v>-2248671</v>
       </c>
     </row>
     <row r="27">
@@ -9552,14 +9555,14 @@
           <t xml:space="preserve">    2028</t>
         </is>
       </c>
-      <c r="C27" s="79" t="n">
-        <v>-3820488</v>
+      <c r="C27" s="97" t="n">
+        <v>-3817948</v>
       </c>
       <c r="D27" s="79" t="n">
         <v>857334</v>
       </c>
       <c r="E27" s="79" t="n">
-        <v>4865694</v>
+        <v>4845178</v>
       </c>
     </row>
     <row r="28">
@@ -9568,14 +9571,14 @@
           <t xml:space="preserve">    2029</t>
         </is>
       </c>
-      <c r="C28" s="79" t="n">
-        <v>-2441609</v>
+      <c r="C28" s="97" t="n">
+        <v>-2405574</v>
       </c>
       <c r="D28" s="79" t="n">
         <v>17475568</v>
       </c>
       <c r="E28" s="79" t="n">
-        <v>36659952</v>
+        <v>36734121</v>
       </c>
     </row>
     <row r="29">
@@ -9584,14 +9587,14 @@
           <t>EBITDA 2030</t>
         </is>
       </c>
-      <c r="C29" s="95" t="n">
-        <v>-1333437</v>
+      <c r="C29" s="130" t="n">
+        <v>-1282047</v>
       </c>
       <c r="D29" s="95" t="n">
         <v>33572021</v>
       </c>
       <c r="E29" s="95" t="n">
-        <v>55061938</v>
+        <v>55082206</v>
       </c>
     </row>
     <row r="30">
@@ -9611,11 +9614,6 @@
       <c r="E30" s="96" t="n">
         <v>2028</v>
       </c>
-      <c r="G30" s="87" t="inlineStr">
-        <is>
-          <t>The downside makes a loss in all five years.</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="inlineStr">
@@ -9648,13 +9646,13 @@
         </is>
       </c>
       <c r="C33" s="97" t="n">
-        <v>-4567386</v>
+        <v>-4508545</v>
       </c>
       <c r="D33" s="79" t="n">
         <v>598473</v>
       </c>
       <c r="E33" s="79" t="n">
-        <v>1164774</v>
+        <v>1183542</v>
       </c>
     </row>
     <row r="34">
@@ -9686,13 +9684,13 @@
         </is>
       </c>
       <c r="C35" s="99" t="n">
-        <v>-7.589568510505514</v>
+        <v>-7.488894893169804</v>
       </c>
       <c r="D35" s="100" t="n">
         <v>2.332960196728448</v>
       </c>
       <c r="E35" s="100" t="n">
-        <v>4.265850160793888</v>
+        <v>4.334583017590123</v>
       </c>
       <c r="G35" s="87" t="inlineStr">
         <is>
@@ -9707,13 +9705,13 @@
         </is>
       </c>
       <c r="C36" s="94" t="n">
-        <v>2.520783120063228</v>
+        <v>2.501191143594139</v>
       </c>
       <c r="D36" s="94" t="n">
         <v>0.8007288929022359</v>
       </c>
       <c r="E36" s="94" t="n">
-        <v>0.6121700344597338</v>
+        <v>0.605921183591093</v>
       </c>
     </row>
     <row r="37">
@@ -9724,7 +9722,7 @@
       </c>
       <c r="C37" s="92" t="inlineStr">
         <is>
-          <t>Yes, EUR4.6m more</t>
+          <t>Yes, EUR4.5m more</t>
         </is>
       </c>
       <c r="D37" s="93" t="inlineStr">
@@ -9739,7 +9737,7 @@
       </c>
       <c r="G37" s="87" t="inlineStr">
         <is>
-          <t>The downside is EUR4.6m short at its lowest point, in Dec 2029.</t>
+          <t>The downside is EUR4.5m short at its lowest point, in Dec 2029.</t>
         </is>
       </c>
     </row>
@@ -9807,13 +9805,13 @@
         <v>2027</v>
       </c>
       <c r="C85" s="103" t="n">
-        <v>-2729582</v>
+        <v>-2729157</v>
       </c>
       <c r="D85" s="103" t="n">
         <v>-2495962</v>
       </c>
       <c r="E85" s="103" t="n">
-        <v>-2255860</v>
+        <v>-2248671</v>
       </c>
     </row>
     <row r="86">
@@ -9821,13 +9819,13 @@
         <v>2028</v>
       </c>
       <c r="C86" s="103" t="n">
-        <v>-3820488</v>
+        <v>-3817948</v>
       </c>
       <c r="D86" s="103" t="n">
         <v>857334</v>
       </c>
       <c r="E86" s="103" t="n">
-        <v>4865694</v>
+        <v>4845178</v>
       </c>
     </row>
     <row r="87">
@@ -9835,13 +9833,13 @@
         <v>2029</v>
       </c>
       <c r="C87" s="103" t="n">
-        <v>-2441609</v>
+        <v>-2405574</v>
       </c>
       <c r="D87" s="103" t="n">
         <v>17475568</v>
       </c>
       <c r="E87" s="103" t="n">
-        <v>36659952</v>
+        <v>36734121</v>
       </c>
     </row>
     <row r="88">
@@ -9849,13 +9847,13 @@
         <v>2030</v>
       </c>
       <c r="C88" s="103" t="n">
-        <v>-1333437</v>
+        <v>-1282047</v>
       </c>
       <c r="D88" s="103" t="n">
         <v>33572021</v>
       </c>
       <c r="E88" s="103" t="n">
-        <v>55061938</v>
+        <v>55082206</v>
       </c>
     </row>
     <row r="91">
@@ -10079,13 +10077,13 @@
         </is>
       </c>
       <c r="C104" s="103" t="n">
-        <v>2579125</v>
+        <v>2579135</v>
       </c>
       <c r="D104" s="103" t="n">
         <v>2759514</v>
       </c>
       <c r="E104" s="103" t="n">
-        <v>2767288</v>
+        <v>2767289</v>
       </c>
     </row>
     <row r="105">
@@ -10095,13 +10093,13 @@
         </is>
       </c>
       <c r="C105" s="103" t="n">
-        <v>2379343</v>
+        <v>2379381</v>
       </c>
       <c r="D105" s="103" t="n">
         <v>2577895</v>
       </c>
       <c r="E105" s="103" t="n">
-        <v>2817613</v>
+        <v>2817616</v>
       </c>
     </row>
     <row r="106">
@@ -10111,13 +10109,13 @@
         </is>
       </c>
       <c r="C106" s="103" t="n">
-        <v>2190785</v>
+        <v>2190850</v>
       </c>
       <c r="D106" s="103" t="n">
         <v>2407582</v>
       </c>
       <c r="E106" s="103" t="n">
-        <v>2680933</v>
+        <v>2680940</v>
       </c>
     </row>
     <row r="107">
@@ -10127,13 +10125,13 @@
         </is>
       </c>
       <c r="C107" s="103" t="n">
-        <v>1972669</v>
+        <v>1972761</v>
       </c>
       <c r="D107" s="103" t="n">
         <v>2221732</v>
       </c>
       <c r="E107" s="103" t="n">
-        <v>2527791</v>
+        <v>2541738</v>
       </c>
     </row>
     <row r="108">
@@ -10143,13 +10141,13 @@
         </is>
       </c>
       <c r="C108" s="103" t="n">
-        <v>1763425</v>
+        <v>1763544</v>
       </c>
       <c r="D108" s="103" t="n">
         <v>2043791</v>
       </c>
       <c r="E108" s="103" t="n">
-        <v>2388162</v>
+        <v>2390540</v>
       </c>
     </row>
     <row r="109">
@@ -10159,13 +10157,13 @@
         </is>
       </c>
       <c r="C109" s="103" t="n">
-        <v>1546550</v>
+        <v>1546701</v>
       </c>
       <c r="D109" s="103" t="n">
         <v>1850031</v>
       </c>
       <c r="E109" s="103" t="n">
-        <v>2221565</v>
+        <v>2223953</v>
       </c>
     </row>
     <row r="110">
@@ -10175,13 +10173,13 @@
         </is>
       </c>
       <c r="C110" s="103" t="n">
-        <v>1326345</v>
+        <v>1326538</v>
       </c>
       <c r="D110" s="103" t="n">
         <v>1667602</v>
       </c>
       <c r="E110" s="103" t="n">
-        <v>2058388</v>
+        <v>2060785</v>
       </c>
     </row>
     <row r="111">
@@ -10191,13 +10189,13 @@
         </is>
       </c>
       <c r="C111" s="103" t="n">
-        <v>1102104</v>
+        <v>1102338</v>
       </c>
       <c r="D111" s="103" t="n">
         <v>1451083</v>
       </c>
       <c r="E111" s="103" t="n">
-        <v>1873704</v>
+        <v>1890047</v>
       </c>
     </row>
     <row r="112">
@@ -10207,13 +10205,13 @@
         </is>
       </c>
       <c r="C112" s="103" t="n">
-        <v>875167</v>
+        <v>875442</v>
       </c>
       <c r="D112" s="103" t="n">
         <v>1254705</v>
       </c>
       <c r="E112" s="103" t="n">
-        <v>1708259</v>
+        <v>1713041</v>
       </c>
     </row>
     <row r="113">
@@ -10223,13 +10221,13 @@
         </is>
       </c>
       <c r="C113" s="103" t="n">
-        <v>644200</v>
+        <v>644516</v>
       </c>
       <c r="D113" s="103" t="n">
         <v>1039418</v>
       </c>
       <c r="E113" s="103" t="n">
-        <v>1515595</v>
+        <v>1520393</v>
       </c>
     </row>
     <row r="114">
@@ -10239,13 +10237,13 @@
         </is>
       </c>
       <c r="C114" s="103" t="n">
-        <v>391968</v>
+        <v>392326</v>
       </c>
       <c r="D114" s="103" t="n">
         <v>835191</v>
       </c>
       <c r="E114" s="103" t="n">
-        <v>1348375</v>
+        <v>1353189</v>
       </c>
     </row>
     <row r="115">
@@ -10255,13 +10253,13 @@
         </is>
       </c>
       <c r="C115" s="103" t="n">
-        <v>144512</v>
+        <v>144911</v>
       </c>
       <c r="D115" s="103" t="n">
         <v>598473</v>
       </c>
       <c r="E115" s="103" t="n">
-        <v>1164774</v>
+        <v>1183542</v>
       </c>
     </row>
     <row r="116">
@@ -10271,13 +10269,13 @@
         </is>
       </c>
       <c r="C116" s="103" t="n">
-        <v>131833</v>
+        <v>132219</v>
       </c>
       <c r="D116" s="103" t="n">
         <v>902957</v>
       </c>
       <c r="E116" s="103" t="n">
-        <v>2024372</v>
+        <v>2031671</v>
       </c>
     </row>
     <row r="117">
@@ -10287,13 +10285,13 @@
         </is>
       </c>
       <c r="C117" s="103" t="n">
-        <v>-158842</v>
+        <v>-158421</v>
       </c>
       <c r="D117" s="103" t="n">
         <v>981993</v>
       </c>
       <c r="E117" s="103" t="n">
-        <v>2410851</v>
+        <v>2430882</v>
       </c>
     </row>
     <row r="118">
@@ -10303,13 +10301,13 @@
         </is>
       </c>
       <c r="C118" s="103" t="n">
-        <v>-447314</v>
+        <v>-446858</v>
       </c>
       <c r="D118" s="103" t="n">
         <v>1056111</v>
       </c>
       <c r="E118" s="103" t="n">
-        <v>2813958</v>
+        <v>2826492</v>
       </c>
     </row>
     <row r="119">
@@ -10319,13 +10317,13 @@
         </is>
       </c>
       <c r="C119" s="103" t="n">
-        <v>-738893</v>
+        <v>-738402</v>
       </c>
       <c r="D119" s="103" t="n">
         <v>1143179</v>
       </c>
       <c r="E119" s="103" t="n">
-        <v>3188881</v>
+        <v>3214154</v>
       </c>
     </row>
     <row r="120">
@@ -10335,13 +10333,13 @@
         </is>
       </c>
       <c r="C120" s="103" t="n">
-        <v>-1052806</v>
+        <v>-1052275</v>
       </c>
       <c r="D120" s="103" t="n">
         <v>1235044</v>
       </c>
       <c r="E120" s="103" t="n">
-        <v>3627896</v>
+        <v>3658295</v>
       </c>
     </row>
     <row r="121">
@@ -10351,13 +10349,13 @@
         </is>
       </c>
       <c r="C121" s="103" t="n">
-        <v>-1355177</v>
+        <v>-1354598</v>
       </c>
       <c r="D121" s="103" t="n">
         <v>1359355</v>
       </c>
       <c r="E121" s="103" t="n">
-        <v>4056008</v>
+        <v>4078924</v>
       </c>
     </row>
     <row r="122">
@@ -10367,13 +10365,13 @@
         </is>
       </c>
       <c r="C122" s="103" t="n">
-        <v>-1655316</v>
+        <v>-1654688</v>
       </c>
       <c r="D122" s="103" t="n">
         <v>1440338</v>
       </c>
       <c r="E122" s="103" t="n">
-        <v>4518368</v>
+        <v>4550618</v>
       </c>
     </row>
     <row r="123">
@@ -10383,13 +10381,13 @@
         </is>
       </c>
       <c r="C123" s="103" t="n">
-        <v>-1972676</v>
+        <v>-1972000</v>
       </c>
       <c r="D123" s="103" t="n">
         <v>1556854</v>
       </c>
       <c r="E123" s="103" t="n">
-        <v>4993001</v>
+        <v>5017510</v>
       </c>
     </row>
     <row r="124">
@@ -10399,13 +10397,13 @@
         </is>
       </c>
       <c r="C124" s="103" t="n">
-        <v>-2267642</v>
+        <v>-2252769</v>
       </c>
       <c r="D124" s="103" t="n">
         <v>1658601</v>
       </c>
       <c r="E124" s="103" t="n">
-        <v>5492003</v>
+        <v>5476478</v>
       </c>
     </row>
     <row r="125">
@@ -10415,13 +10413,13 @@
         </is>
       </c>
       <c r="C125" s="103" t="n">
-        <v>-2558774</v>
+        <v>-2556035</v>
       </c>
       <c r="D125" s="103" t="n">
         <v>1782269</v>
       </c>
       <c r="E125" s="103" t="n">
-        <v>6007863</v>
+        <v>5995834</v>
       </c>
     </row>
     <row r="126">
@@ -10431,13 +10429,13 @@
         </is>
       </c>
       <c r="C126" s="103" t="n">
-        <v>-2859839</v>
+        <v>-2857031</v>
       </c>
       <c r="D126" s="103" t="n">
         <v>1891930</v>
       </c>
       <c r="E126" s="103" t="n">
-        <v>6441554</v>
+        <v>6444216</v>
       </c>
     </row>
     <row r="127">
@@ -10447,13 +10445,13 @@
         </is>
       </c>
       <c r="C127" s="103" t="n">
-        <v>-3178089</v>
+        <v>-3175215</v>
       </c>
       <c r="D127" s="103" t="n">
         <v>2024363</v>
       </c>
       <c r="E127" s="103" t="n">
-        <v>6850281</v>
+        <v>6848269</v>
       </c>
     </row>
     <row r="128">
@@ -10463,13 +10461,13 @@
         </is>
       </c>
       <c r="C128" s="103" t="n">
-        <v>-2837073</v>
+        <v>-2834201</v>
       </c>
       <c r="D128" s="103" t="n">
         <v>3532765</v>
       </c>
       <c r="E128" s="103" t="n">
-        <v>9279515</v>
+        <v>9277554</v>
       </c>
     </row>
     <row r="129">
@@ -10479,13 +10477,13 @@
         </is>
       </c>
       <c r="C129" s="103" t="n">
-        <v>-3024311</v>
+        <v>-3021321</v>
       </c>
       <c r="D129" s="103" t="n">
         <v>4844147</v>
       </c>
       <c r="E129" s="103" t="n">
-        <v>11457157</v>
+        <v>11474879</v>
       </c>
     </row>
     <row r="130">
@@ -10495,13 +10493,13 @@
         </is>
       </c>
       <c r="C130" s="103" t="n">
-        <v>-3200488</v>
+        <v>-3170508</v>
       </c>
       <c r="D130" s="103" t="n">
         <v>6125526</v>
       </c>
       <c r="E130" s="103" t="n">
-        <v>13603843</v>
+        <v>13602535</v>
       </c>
     </row>
     <row r="131">
@@ -10511,13 +10509,13 @@
         </is>
       </c>
       <c r="C131" s="103" t="n">
-        <v>-3381231</v>
+        <v>-3371205</v>
       </c>
       <c r="D131" s="103" t="n">
         <v>7174919</v>
       </c>
       <c r="E131" s="103" t="n">
-        <v>15793573</v>
+        <v>15806769</v>
       </c>
     </row>
     <row r="132">
@@ -10527,13 +10525,13 @@
         </is>
       </c>
       <c r="C132" s="103" t="n">
-        <v>-3536836</v>
+        <v>-3526645</v>
       </c>
       <c r="D132" s="103" t="n">
         <v>8244032</v>
       </c>
       <c r="E132" s="103" t="n">
-        <v>18080708</v>
+        <v>18096715</v>
       </c>
     </row>
     <row r="133">
@@ -10543,13 +10541,13 @@
         </is>
       </c>
       <c r="C133" s="103" t="n">
-        <v>-3681724</v>
+        <v>-3671364</v>
       </c>
       <c r="D133" s="103" t="n">
         <v>9358102</v>
       </c>
       <c r="E133" s="103" t="n">
-        <v>20418013</v>
+        <v>20448753</v>
       </c>
     </row>
     <row r="134">
@@ -10559,13 +10557,13 @@
         </is>
       </c>
       <c r="C134" s="103" t="n">
-        <v>-3849582</v>
+        <v>-3812181</v>
       </c>
       <c r="D134" s="103" t="n">
         <v>10494721</v>
       </c>
       <c r="E134" s="103" t="n">
-        <v>22770348</v>
+        <v>22791893</v>
       </c>
     </row>
     <row r="135">
@@ -10575,13 +10573,13 @@
         </is>
       </c>
       <c r="C135" s="103" t="n">
-        <v>-4007418</v>
+        <v>-3963061</v>
       </c>
       <c r="D135" s="103" t="n">
         <v>11676659</v>
       </c>
       <c r="E135" s="103" t="n">
-        <v>25209459</v>
+        <v>25240895</v>
       </c>
     </row>
     <row r="136">
@@ -10591,13 +10589,13 @@
         </is>
       </c>
       <c r="C136" s="103" t="n">
-        <v>-4130839</v>
+        <v>-4106360</v>
       </c>
       <c r="D136" s="103" t="n">
         <v>12894819</v>
       </c>
       <c r="E136" s="103" t="n">
-        <v>27738550</v>
+        <v>27775251</v>
       </c>
     </row>
     <row r="137">
@@ -10607,13 +10605,13 @@
         </is>
       </c>
       <c r="C137" s="103" t="n">
-        <v>-4271872</v>
+        <v>-4247153</v>
       </c>
       <c r="D137" s="103" t="n">
         <v>14148474</v>
       </c>
       <c r="E137" s="103" t="n">
-        <v>30320520</v>
+        <v>30369877</v>
       </c>
     </row>
     <row r="138">
@@ -10623,13 +10621,13 @@
         </is>
       </c>
       <c r="C138" s="103" t="n">
-        <v>-4424688</v>
+        <v>-4372865</v>
       </c>
       <c r="D138" s="103" t="n">
         <v>15422088</v>
       </c>
       <c r="E138" s="103" t="n">
-        <v>32878086</v>
+        <v>32917934</v>
       </c>
     </row>
     <row r="139">
@@ -10639,13 +10637,13 @@
         </is>
       </c>
       <c r="C139" s="103" t="n">
-        <v>-4567386</v>
+        <v>-4508545</v>
       </c>
       <c r="D139" s="103" t="n">
         <v>16724030</v>
       </c>
       <c r="E139" s="103" t="n">
-        <v>35610077</v>
+        <v>35659837</v>
       </c>
     </row>
     <row r="140">
@@ -10655,13 +10653,13 @@
         </is>
       </c>
       <c r="C140" s="103" t="n">
-        <v>-4057563</v>
+        <v>-3977589</v>
       </c>
       <c r="D140" s="103" t="n">
         <v>19263294</v>
       </c>
       <c r="E140" s="103" t="n">
-        <v>39463477</v>
+        <v>39508704</v>
       </c>
     </row>
     <row r="141">
@@ -10671,13 +10669,13 @@
         </is>
       </c>
       <c r="C141" s="103" t="n">
-        <v>-4128416</v>
+        <v>-4041204</v>
       </c>
       <c r="D141" s="103" t="n">
         <v>21224807</v>
       </c>
       <c r="E141" s="103" t="n">
-        <v>42601459</v>
+        <v>42646793</v>
       </c>
     </row>
     <row r="142">
@@ -10687,13 +10685,13 @@
         </is>
       </c>
       <c r="C142" s="103" t="n">
-        <v>-4157202</v>
+        <v>-4099841</v>
       </c>
       <c r="D142" s="103" t="n">
         <v>23249495</v>
       </c>
       <c r="E142" s="103" t="n">
-        <v>45736029</v>
+        <v>45781470</v>
       </c>
     </row>
     <row r="143">
@@ -10703,13 +10701,13 @@
         </is>
       </c>
       <c r="C143" s="103" t="n">
-        <v>-4218225</v>
+        <v>-4159825</v>
       </c>
       <c r="D143" s="103" t="n">
         <v>25318025</v>
       </c>
       <c r="E143" s="103" t="n">
-        <v>49403648</v>
+        <v>49449197</v>
       </c>
     </row>
     <row r="144">
@@ -10719,13 +10717,13 @@
         </is>
       </c>
       <c r="C144" s="103" t="n">
-        <v>-4302932</v>
+        <v>-4243475</v>
       </c>
       <c r="D144" s="103" t="n">
         <v>27473234</v>
       </c>
       <c r="E144" s="103" t="n">
-        <v>52794803</v>
+        <v>52840462</v>
       </c>
     </row>
     <row r="145">
@@ -10735,13 +10733,13 @@
         </is>
       </c>
       <c r="C145" s="103" t="n">
-        <v>-4332217</v>
+        <v>-4271682</v>
       </c>
       <c r="D145" s="103" t="n">
         <v>29643948</v>
       </c>
       <c r="E145" s="103" t="n">
-        <v>56182836</v>
+        <v>56228606</v>
       </c>
     </row>
     <row r="146">
@@ -10751,13 +10749,13 @@
         </is>
       </c>
       <c r="C146" s="103" t="n">
-        <v>-4389146</v>
+        <v>-4300593</v>
       </c>
       <c r="D146" s="103" t="n">
         <v>31880803</v>
       </c>
       <c r="E146" s="103" t="n">
-        <v>59520194</v>
+        <v>59583339</v>
       </c>
     </row>
     <row r="147">
@@ -10767,13 +10765,13 @@
         </is>
       </c>
       <c r="C147" s="103" t="n">
-        <v>-4415949</v>
+        <v>-4309866</v>
       </c>
       <c r="D147" s="103" t="n">
         <v>34140812</v>
       </c>
       <c r="E147" s="103" t="n">
-        <v>63478644</v>
+        <v>63533209</v>
       </c>
     </row>
     <row r="148">
@@ -10783,13 +10781,13 @@
         </is>
       </c>
       <c r="C148" s="103" t="n">
-        <v>-4413906</v>
+        <v>-4297150</v>
       </c>
       <c r="D148" s="103" t="n">
         <v>36320804</v>
       </c>
       <c r="E148" s="103" t="n">
-        <v>67100120</v>
+        <v>67154799</v>
       </c>
     </row>
     <row r="149">
@@ -10799,13 +10797,13 @@
         </is>
       </c>
       <c r="C149" s="103" t="n">
-        <v>-4399406</v>
+        <v>-4311935</v>
       </c>
       <c r="D149" s="103" t="n">
         <v>38529724</v>
       </c>
       <c r="E149" s="103" t="n">
-        <v>70736151</v>
+        <v>70790943</v>
       </c>
     </row>
     <row r="150">
@@ -10815,13 +10813,13 @@
         </is>
       </c>
       <c r="C150" s="103" t="n">
-        <v>-4389397</v>
+        <v>-4300717</v>
       </c>
       <c r="D150" s="103" t="n">
         <v>40725588</v>
       </c>
       <c r="E150" s="103" t="n">
-        <v>74336178</v>
+        <v>74391084</v>
       </c>
     </row>
     <row r="151">
@@ -10831,13 +10829,13 @@
         </is>
       </c>
       <c r="C151" s="103" t="n">
-        <v>-4391251</v>
+        <v>-4301342</v>
       </c>
       <c r="D151" s="103" t="n">
         <v>42900274</v>
       </c>
       <c r="E151" s="103" t="n">
-        <v>77919568</v>
+        <v>77984460</v>
       </c>
     </row>
   </sheetData>
